--- a/03_BOM/BEE_1012 PAY-EXP V100 BOM.xlsx
+++ b/03_BOM/BEE_1012 PAY-EXP V100 BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Altium_WorkSpace\2_Satellite_1\Satellite_4U_EXP_HW_1.0.0\03_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E3CB06-E29A-460C-83CE-30D4862C892B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E1B91F-CA2E-4467-9479-D933B434CA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92AD7317-08C2-4C96-BE61-09489C3F9F0C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="508">
   <si>
     <t>Comment</t>
   </si>
@@ -335,9 +335,6 @@
     <t>R109</t>
   </si>
   <si>
-    <t>ERJ-2GEJ106X</t>
-  </si>
-  <si>
     <t>10uF/20V</t>
   </si>
   <si>
@@ -1563,6 +1560,9 @@
   </si>
   <si>
     <t>DIODE</t>
+  </si>
+  <si>
+    <t>ERJ-2GEJ105X</t>
   </si>
 </sst>
 </file>
@@ -1659,23 +1659,23 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2018,7 +2018,7 @@
     <col min="2" max="2" width="28" style="1" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="16" customWidth="1"/>
+    <col min="5" max="5" width="5.7109375" style="13" customWidth="1"/>
     <col min="6" max="6" width="7.85546875" style="1" customWidth="1"/>
     <col min="7" max="8" width="19" style="1" customWidth="1"/>
     <col min="9" max="9" width="16.28515625" style="1" customWidth="1"/>
@@ -2040,7 +2040,7 @@
       <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="10" t="s">
@@ -2073,9 +2073,9 @@
         <v>13</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="E2" s="14">
+        <v>504</v>
+      </c>
+      <c r="E2" s="12">
         <v>1</v>
       </c>
       <c r="F2" s="2">
@@ -2106,9 +2106,9 @@
         <v>13</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="E3" s="14">
+        <v>504</v>
+      </c>
+      <c r="E3" s="12">
         <v>1</v>
       </c>
       <c r="F3" s="2">
@@ -2133,15 +2133,15 @@
         <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="E4" s="14">
+        <v>504</v>
+      </c>
+      <c r="E4" s="12">
         <v>10</v>
       </c>
       <c r="F4" s="2">
@@ -2174,9 +2174,9 @@
         <v>13</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="E5" s="14">
+        <v>504</v>
+      </c>
+      <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="2">
@@ -2201,7 +2201,7 @@
         <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>27</v>
@@ -2209,7 +2209,7 @@
       <c r="D6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <v>1</v>
       </c>
       <c r="F6" s="2">
@@ -2234,7 +2234,7 @@
         <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>32</v>
@@ -2242,7 +2242,7 @@
       <c r="D7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="12">
         <v>6</v>
       </c>
       <c r="F7" s="2">
@@ -2277,7 +2277,7 @@
       <c r="D8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="12">
         <v>2</v>
       </c>
       <c r="F8" s="2">
@@ -2304,7 +2304,7 @@
         <v>40</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>41</v>
@@ -2312,7 +2312,7 @@
       <c r="D9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="12">
         <v>108</v>
       </c>
       <c r="F9" s="2">
@@ -2339,7 +2339,7 @@
         <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>43</v>
@@ -2347,7 +2347,7 @@
       <c r="D10" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="12">
         <v>38</v>
       </c>
       <c r="F10" s="2">
@@ -2374,7 +2374,7 @@
         <v>40</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>43</v>
@@ -2382,7 +2382,7 @@
       <c r="D11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="12">
         <v>50</v>
       </c>
       <c r="F11" s="2">
@@ -2409,7 +2409,7 @@
         <v>46</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>27</v>
@@ -2417,7 +2417,7 @@
       <c r="D12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="12">
         <v>5</v>
       </c>
       <c r="F12" s="2">
@@ -2452,7 +2452,7 @@
       <c r="D13" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="12">
         <v>3</v>
       </c>
       <c r="F13" s="2">
@@ -2487,7 +2487,7 @@
       <c r="D14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="12">
         <v>3</v>
       </c>
       <c r="F14" s="2">
@@ -2520,9 +2520,9 @@
         <v>56</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="E15" s="14">
+        <v>506</v>
+      </c>
+      <c r="E15" s="12">
         <v>24</v>
       </c>
       <c r="F15" s="2">
@@ -2557,7 +2557,7 @@
       <c r="D16" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="12">
         <v>29</v>
       </c>
       <c r="F16" s="2">
@@ -2590,9 +2590,9 @@
         <v>65</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="E17" s="14">
+        <v>505</v>
+      </c>
+      <c r="E17" s="12">
         <v>4</v>
       </c>
       <c r="F17" s="2">
@@ -2627,7 +2627,7 @@
       <c r="D18" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="12">
         <v>7</v>
       </c>
       <c r="F18" s="2">
@@ -2662,7 +2662,7 @@
       <c r="D19" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="12">
         <v>1</v>
       </c>
       <c r="F19" s="2">
@@ -2695,7 +2695,7 @@
       <c r="D20" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="12">
         <v>14</v>
       </c>
       <c r="F20" s="2">
@@ -2722,7 +2722,7 @@
         <v>80</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>27</v>
@@ -2730,7 +2730,7 @@
       <c r="D21" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="12">
         <v>11</v>
       </c>
       <c r="F21" s="2">
@@ -2765,7 +2765,7 @@
       <c r="D22" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="12">
         <v>1</v>
       </c>
       <c r="F22" s="2">
@@ -2790,7 +2790,7 @@
         <v>85</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>32</v>
@@ -2798,7 +2798,7 @@
       <c r="D23" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="12">
         <v>3</v>
       </c>
       <c r="F23" s="2">
@@ -2814,7 +2814,7 @@
         <v>30</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K23" s="2"/>
     </row>
@@ -2823,7 +2823,7 @@
         <v>85</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>27</v>
@@ -2831,7 +2831,7 @@
       <c r="D24" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="12">
         <v>61</v>
       </c>
       <c r="F24" s="2">
@@ -2866,7 +2866,7 @@
       <c r="D25" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="12">
         <v>29</v>
       </c>
       <c r="F25" s="2">
@@ -2901,7 +2901,7 @@
       <c r="D26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="12">
         <v>1</v>
       </c>
       <c r="F26" s="2">
@@ -2926,7 +2926,7 @@
         <v>93</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>27</v>
@@ -2934,7 +2934,7 @@
       <c r="D27" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="12">
         <v>113</v>
       </c>
       <c r="F27" s="2">
@@ -2961,7 +2961,7 @@
         <v>93</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>32</v>
@@ -2969,7 +2969,7 @@
       <c r="D28" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="12">
         <v>11</v>
       </c>
       <c r="F28" s="2">
@@ -3004,7 +3004,7 @@
       <c r="D29" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="12">
         <v>1</v>
       </c>
       <c r="F29" s="2">
@@ -3020,31 +3020,31 @@
         <v>30</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>98</v>
+        <v>507</v>
       </c>
       <c r="K29" s="2"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C30" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="D30" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="E30" s="12">
+        <v>5</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="E30" s="14">
-        <v>5</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>103</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>15</v>
@@ -3053,7 +3053,7 @@
         <v>38</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>14</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>41</v>
@@ -3072,7 +3072,7 @@
       <c r="D31" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31" s="12">
         <v>3</v>
       </c>
       <c r="F31" s="2">
@@ -3088,7 +3088,7 @@
         <v>44</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>14</v>
@@ -3096,10 +3096,10 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>27</v>
@@ -3107,7 +3107,7 @@
       <c r="D32" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="12">
         <v>2</v>
       </c>
       <c r="F32" s="2">
@@ -3123,7 +3123,7 @@
         <v>75</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>14</v>
@@ -3131,10 +3131,10 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>32</v>
@@ -3142,7 +3142,7 @@
       <c r="D33" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E33" s="12">
         <v>2</v>
       </c>
       <c r="F33" s="2">
@@ -3158,7 +3158,7 @@
         <v>30</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>14</v>
@@ -3166,10 +3166,10 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>43</v>
@@ -3177,7 +3177,7 @@
       <c r="D34" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E34" s="12">
         <v>6</v>
       </c>
       <c r="F34" s="2">
@@ -3190,10 +3190,10 @@
         <v>15</v>
       </c>
       <c r="I34" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="J34" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>117</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>14</v>
@@ -3201,10 +3201,10 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>32</v>
@@ -3212,7 +3212,7 @@
       <c r="D35" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E35" s="14">
+      <c r="E35" s="12">
         <v>2</v>
       </c>
       <c r="F35" s="2">
@@ -3228,59 +3228,59 @@
         <v>30</v>
       </c>
       <c r="J35" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="K35" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
+      <c r="B36" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="C36" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E36" s="15">
+      <c r="E36" s="16">
         <v>16</v>
       </c>
-      <c r="F36" s="15">
-        <v>0</v>
-      </c>
-      <c r="G36" s="12" t="s">
+      <c r="F36" s="16">
+        <v>0</v>
+      </c>
+      <c r="G36" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="H36" s="12" t="s">
+      <c r="H36" s="14" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="K36" s="4"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="14"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="J36" s="7" t="s">
+      <c r="J37" s="8" t="s">
         <v>471</v>
-      </c>
-      <c r="K36" s="4"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="12"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="8" t="s">
-        <v>504</v>
-      </c>
-      <c r="J37" s="8" t="s">
-        <v>472</v>
       </c>
       <c r="K37" s="4" t="s">
         <v>14</v>
@@ -3288,10 +3288,10 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>27</v>
@@ -3299,7 +3299,7 @@
       <c r="D38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E38" s="12">
         <v>133</v>
       </c>
       <c r="F38" s="2">
@@ -3315,7 +3315,7 @@
         <v>30</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>14</v>
@@ -3323,10 +3323,10 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>32</v>
@@ -3334,7 +3334,7 @@
       <c r="D39" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E39" s="14">
+      <c r="E39" s="12">
         <v>82</v>
       </c>
       <c r="F39" s="2">
@@ -3347,10 +3347,10 @@
         <v>15</v>
       </c>
       <c r="I39" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="J39" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>127</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>14</v>
@@ -3358,10 +3358,10 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>35</v>
@@ -3369,7 +3369,7 @@
       <c r="D40" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E40" s="14">
+      <c r="E40" s="12">
         <v>4</v>
       </c>
       <c r="F40" s="2">
@@ -3385,7 +3385,7 @@
         <v>44</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>14</v>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>27</v>
@@ -3404,7 +3404,7 @@
       <c r="D41" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E41" s="14">
+      <c r="E41" s="12">
         <v>15</v>
       </c>
       <c r="F41" s="2">
@@ -3420,7 +3420,7 @@
         <v>30</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>14</v>
@@ -3428,10 +3428,10 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>41</v>
@@ -3439,7 +3439,7 @@
       <c r="D42" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E42" s="14">
+      <c r="E42" s="12">
         <v>12</v>
       </c>
       <c r="F42" s="2">
@@ -3455,7 +3455,7 @@
         <v>38</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>14</v>
@@ -3463,34 +3463,34 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C43" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="D43" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E43" s="12">
+        <v>29</v>
+      </c>
+      <c r="F43" s="2">
+        <v>0</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E43" s="14">
-        <v>29</v>
-      </c>
-      <c r="F43" s="2">
-        <v>0</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I43" s="4" t="s">
+      <c r="J43" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>141</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>14</v>
@@ -3498,10 +3498,10 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>27</v>
@@ -3509,7 +3509,7 @@
       <c r="D44" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E44" s="14">
+      <c r="E44" s="12">
         <v>6</v>
       </c>
       <c r="F44" s="2">
@@ -3525,7 +3525,7 @@
         <v>30</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>14</v>
@@ -3533,10 +3533,10 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>32</v>
@@ -3544,7 +3544,7 @@
       <c r="D45" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E45" s="14">
+      <c r="E45" s="12">
         <v>2</v>
       </c>
       <c r="F45" s="2">
@@ -3560,7 +3560,7 @@
         <v>30</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>14</v>
@@ -3568,10 +3568,10 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>27</v>
@@ -3579,7 +3579,7 @@
       <c r="D46" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E46" s="14">
+      <c r="E46" s="12">
         <v>2</v>
       </c>
       <c r="F46" s="2">
@@ -3592,10 +3592,10 @@
         <v>15</v>
       </c>
       <c r="I46" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J46" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>14</v>
@@ -3603,10 +3603,10 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>27</v>
@@ -3614,7 +3614,7 @@
       <c r="D47" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E47" s="14">
+      <c r="E47" s="12">
         <v>10</v>
       </c>
       <c r="F47" s="2">
@@ -3630,7 +3630,7 @@
         <v>30</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K47" s="4" t="s">
         <v>14</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>27</v>
@@ -3649,7 +3649,7 @@
       <c r="D48" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E48" s="14">
+      <c r="E48" s="12">
         <v>6</v>
       </c>
       <c r="F48" s="2">
@@ -3665,7 +3665,7 @@
         <v>30</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>14</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>41</v>
@@ -3684,7 +3684,7 @@
       <c r="D49" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E49" s="14">
+      <c r="E49" s="12">
         <v>16</v>
       </c>
       <c r="F49" s="2">
@@ -3700,7 +3700,7 @@
         <v>38</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>14</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>32</v>
@@ -3719,7 +3719,7 @@
       <c r="D50" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E50" s="14">
+      <c r="E50" s="12">
         <v>3</v>
       </c>
       <c r="F50" s="2">
@@ -3732,10 +3732,10 @@
         <v>15</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K50" s="4" t="s">
         <v>14</v>
@@ -3743,10 +3743,10 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>32</v>
@@ -3754,7 +3754,7 @@
       <c r="D51" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E51" s="14">
+      <c r="E51" s="12">
         <v>2</v>
       </c>
       <c r="F51" s="2">
@@ -3770,7 +3770,7 @@
         <v>75</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K51" s="4" t="s">
         <v>14</v>
@@ -3778,10 +3778,10 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>27</v>
@@ -3789,7 +3789,7 @@
       <c r="D52" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E52" s="14">
+      <c r="E52" s="12">
         <v>7</v>
       </c>
       <c r="F52" s="2">
@@ -3805,7 +3805,7 @@
         <v>30</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>14</v>
@@ -3813,100 +3813,100 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="D53" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="E53" s="12">
+        <v>1</v>
+      </c>
+      <c r="F53" s="2">
+        <v>0</v>
+      </c>
+      <c r="G53" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="E53" s="14">
-        <v>1</v>
-      </c>
-      <c r="F53" s="2">
-        <v>0</v>
-      </c>
-      <c r="G53" s="4" t="s">
+      <c r="H53" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="H53" s="4" t="s">
+      <c r="I53" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="I53" s="4" t="s">
+      <c r="J53" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>175</v>
       </c>
       <c r="K53" s="2"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="D54" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54" s="12">
+        <v>1</v>
+      </c>
+      <c r="F54" s="2">
+        <v>0</v>
+      </c>
+      <c r="G54" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D54" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E54" s="14">
-        <v>1</v>
-      </c>
-      <c r="F54" s="2">
-        <v>0</v>
-      </c>
-      <c r="G54" s="4" t="s">
+      <c r="H54" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="J54" s="4" t="s">
         <v>179</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>180</v>
       </c>
       <c r="K54" s="2"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C55" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="D55" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" s="12">
+        <v>3</v>
+      </c>
+      <c r="F55" s="2">
+        <v>0</v>
+      </c>
+      <c r="G55" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E55" s="14">
-        <v>3</v>
-      </c>
-      <c r="F55" s="2">
-        <v>0</v>
-      </c>
-      <c r="G55" s="4" t="s">
+      <c r="H55" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="J55" s="4" t="s">
         <v>184</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>185</v>
       </c>
       <c r="K55" s="4" t="s">
         <v>14</v>
@@ -3914,34 +3914,34 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C56" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="D56" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="12">
+        <v>2</v>
+      </c>
+      <c r="F56" s="2">
+        <v>0</v>
+      </c>
+      <c r="G56" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="D56" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56" s="14">
-        <v>2</v>
-      </c>
-      <c r="F56" s="2">
-        <v>0</v>
-      </c>
-      <c r="G56" s="4" t="s">
+      <c r="H56" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="J56" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I56" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>190</v>
       </c>
       <c r="K56" s="4" t="s">
         <v>14</v>
@@ -3949,34 +3949,34 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="C57" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="D57" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="12">
+        <v>4</v>
+      </c>
+      <c r="F57" s="2">
+        <v>0</v>
+      </c>
+      <c r="G57" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="D57" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57" s="14">
-        <v>4</v>
-      </c>
-      <c r="F57" s="2">
-        <v>0</v>
-      </c>
-      <c r="G57" s="4" t="s">
+      <c r="H57" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="J57" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>195</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>14</v>
@@ -3984,34 +3984,34 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C58" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="D58" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="12">
+        <v>2</v>
+      </c>
+      <c r="F58" s="2">
+        <v>0</v>
+      </c>
+      <c r="G58" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="D58" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E58" s="14">
-        <v>2</v>
-      </c>
-      <c r="F58" s="2">
-        <v>0</v>
-      </c>
-      <c r="G58" s="4" t="s">
+      <c r="H58" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="J58" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I58" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>200</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>14</v>
@@ -4019,34 +4019,34 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="C59" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="D59" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" s="12">
+        <v>2</v>
+      </c>
+      <c r="F59" s="2">
+        <v>0</v>
+      </c>
+      <c r="G59" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="D59" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E59" s="14">
-        <v>2</v>
-      </c>
-      <c r="F59" s="2">
-        <v>0</v>
-      </c>
-      <c r="G59" s="4" t="s">
+      <c r="H59" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="J59" s="4" t="s">
         <v>204</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I59" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="J59" s="4" t="s">
-        <v>205</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>14</v>
@@ -4054,133 +4054,133 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C60" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="D60" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="E60" s="12">
+        <v>1</v>
+      </c>
+      <c r="F60" s="2">
+        <v>0</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="H60" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="E60" s="14">
-        <v>1</v>
-      </c>
-      <c r="F60" s="2">
-        <v>0</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="H60" s="4" t="s">
+      <c r="I60" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="J60" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="I60" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="J60" s="4" t="s">
-        <v>211</v>
       </c>
       <c r="K60" s="2"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="C61" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="D61" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="12">
+        <v>1</v>
+      </c>
+      <c r="F61" s="2">
+        <v>0</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="J61" s="4" t="s">
         <v>214</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" s="14">
-        <v>1</v>
-      </c>
-      <c r="F61" s="2">
-        <v>0</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>215</v>
       </c>
       <c r="K61" s="2"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="C62" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="D62" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" s="12">
+        <v>1</v>
+      </c>
+      <c r="F62" s="2">
+        <v>0</v>
+      </c>
+      <c r="G62" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="D62" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E62" s="14">
-        <v>1</v>
-      </c>
-      <c r="F62" s="2">
-        <v>0</v>
-      </c>
-      <c r="G62" s="4" t="s">
+      <c r="H62" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="J62" s="4" t="s">
         <v>219</v>
-      </c>
-      <c r="H62" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I62" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>220</v>
       </c>
       <c r="K62" s="2"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="C63" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="D63" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="12">
+        <v>13</v>
+      </c>
+      <c r="F63" s="2">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="D63" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E63" s="14">
-        <v>13</v>
-      </c>
-      <c r="F63" s="2">
-        <v>0</v>
-      </c>
-      <c r="G63" s="4" t="s">
+      <c r="H63" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="J63" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I63" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>225</v>
       </c>
       <c r="K63" s="4" t="s">
         <v>14</v>
@@ -4188,67 +4188,67 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="C64" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="D64" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="12">
+        <v>1</v>
+      </c>
+      <c r="F64" s="2">
+        <v>0</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="J64" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64" s="14">
-        <v>1</v>
-      </c>
-      <c r="F64" s="2">
-        <v>0</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I64" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>229</v>
       </c>
       <c r="K64" s="2"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="C65" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="D65" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="E65" s="12">
+        <v>24</v>
+      </c>
+      <c r="F65" s="2">
+        <v>0</v>
+      </c>
+      <c r="G65" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="E65" s="14">
-        <v>24</v>
-      </c>
-      <c r="F65" s="2">
-        <v>0</v>
-      </c>
-      <c r="G65" s="4" t="s">
+      <c r="H65" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I65" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="H65" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I65" s="4" t="s">
-        <v>235</v>
-      </c>
       <c r="J65" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K65" s="4" t="s">
         <v>14</v>
@@ -4256,34 +4256,34 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="C66" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="D66" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="12">
+        <v>2</v>
+      </c>
+      <c r="F66" s="2">
+        <v>0</v>
+      </c>
+      <c r="G66" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="D66" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="14">
-        <v>2</v>
-      </c>
-      <c r="F66" s="2">
-        <v>0</v>
-      </c>
-      <c r="G66" s="4" t="s">
+      <c r="H66" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I66" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="H66" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I66" s="4" t="s">
-        <v>240</v>
-      </c>
       <c r="J66" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>14</v>
@@ -4291,100 +4291,100 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="C67" s="4" t="s">
         <v>242</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>243</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E67" s="14">
+      <c r="E67" s="12">
         <v>1</v>
       </c>
       <c r="F67" s="2">
         <v>0</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K67" s="2"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="C68" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="D68" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="E68" s="12">
+        <v>1</v>
+      </c>
+      <c r="F68" s="2">
+        <v>0</v>
+      </c>
+      <c r="G68" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="E68" s="14">
-        <v>1</v>
-      </c>
-      <c r="F68" s="2">
-        <v>0</v>
-      </c>
-      <c r="G68" s="4" t="s">
+      <c r="H68" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I68" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="H68" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I68" s="4" t="s">
-        <v>250</v>
-      </c>
       <c r="J68" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K68" s="2"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="C69" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="D69" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="E69" s="12">
+        <v>2</v>
+      </c>
+      <c r="F69" s="2">
+        <v>0</v>
+      </c>
+      <c r="G69" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="E69" s="14">
-        <v>2</v>
-      </c>
-      <c r="F69" s="2">
-        <v>0</v>
-      </c>
-      <c r="G69" s="4" t="s">
+      <c r="H69" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I69" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="H69" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I69" s="4" t="s">
+      <c r="J69" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="J69" s="4" t="s">
-        <v>257</v>
       </c>
       <c r="K69" s="4" t="s">
         <v>14</v>
@@ -4392,58 +4392,58 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="C70" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="D70" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E70" s="12">
+        <v>1</v>
+      </c>
+      <c r="F70" s="2">
+        <v>0</v>
+      </c>
+      <c r="G70" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="D70" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="E70" s="14">
-        <v>1</v>
-      </c>
-      <c r="F70" s="2">
-        <v>0</v>
-      </c>
-      <c r="G70" s="4" t="s">
+      <c r="H70" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I70" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="H70" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I70" s="4" t="s">
+      <c r="J70" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="J70" s="4" t="s">
-        <v>263</v>
       </c>
       <c r="K70" s="2"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="C71" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="D71" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="E71" s="12">
+        <v>4</v>
+      </c>
+      <c r="F71" s="2">
+        <v>0</v>
+      </c>
+      <c r="G71" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="E71" s="14">
-        <v>4</v>
-      </c>
-      <c r="F71" s="2">
-        <v>0</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>268</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>15</v>
@@ -4452,7 +4452,7 @@
         <v>44</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K71" s="4" t="s">
         <v>14</v>
@@ -4460,34 +4460,34 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="C72" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="12">
+        <v>2</v>
+      </c>
+      <c r="F72" s="2">
+        <v>0</v>
+      </c>
+      <c r="G72" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="C72" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E72" s="14">
-        <v>2</v>
-      </c>
-      <c r="F72" s="2">
-        <v>0</v>
-      </c>
-      <c r="G72" s="4" t="s">
+      <c r="H72" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I72" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="H72" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>272</v>
-      </c>
       <c r="J72" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K72" s="4" t="s">
         <v>14</v>
@@ -4495,28 +4495,28 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="C73" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="D73" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" s="12">
+        <v>11</v>
+      </c>
+      <c r="F73" s="2">
+        <v>0</v>
+      </c>
+      <c r="G73" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="D73" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E73" s="14">
-        <v>11</v>
-      </c>
-      <c r="F73" s="2">
-        <v>0</v>
-      </c>
-      <c r="G73" s="4" t="s">
+      <c r="H73" s="4" t="s">
         <v>276</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>277</v>
       </c>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
@@ -4526,10 +4526,10 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>27</v>
@@ -4537,7 +4537,7 @@
       <c r="D74" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E74" s="14">
+      <c r="E74" s="12">
         <v>2</v>
       </c>
       <c r="F74" s="2">
@@ -4561,10 +4561,10 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>32</v>
@@ -4572,7 +4572,7 @@
       <c r="D75" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E75" s="14">
+      <c r="E75" s="12">
         <v>4</v>
       </c>
       <c r="F75" s="2">
@@ -4592,10 +4592,10 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>27</v>
@@ -4603,7 +4603,7 @@
       <c r="D76" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E76" s="14">
+      <c r="E76" s="12">
         <v>6</v>
       </c>
       <c r="F76" s="2">
@@ -4627,10 +4627,10 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>27</v>
@@ -4638,7 +4638,7 @@
       <c r="D77" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E77" s="14">
+      <c r="E77" s="12">
         <v>17</v>
       </c>
       <c r="F77" s="2">
@@ -4662,10 +4662,10 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>32</v>
@@ -4673,7 +4673,7 @@
       <c r="D78" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E78" s="14">
+      <c r="E78" s="12">
         <v>11</v>
       </c>
       <c r="F78" s="2">
@@ -4697,10 +4697,10 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>27</v>
@@ -4708,7 +4708,7 @@
       <c r="D79" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E79" s="14">
+      <c r="E79" s="12">
         <v>1</v>
       </c>
       <c r="F79" s="2">
@@ -4724,172 +4724,172 @@
         <v>30</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K79" s="2"/>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="C80" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="D80" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E80" s="12">
+        <v>1</v>
+      </c>
+      <c r="F80" s="2">
+        <v>0</v>
+      </c>
+      <c r="G80" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="D80" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E80" s="14">
-        <v>1</v>
-      </c>
-      <c r="F80" s="2">
-        <v>0</v>
-      </c>
-      <c r="G80" s="4" t="s">
+      <c r="H80" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I80" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="H80" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I80" s="4" t="s">
+      <c r="J80" s="4" t="s">
         <v>287</v>
-      </c>
-      <c r="J80" s="4" t="s">
-        <v>288</v>
       </c>
       <c r="K80" s="2"/>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="C81" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="D81" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" s="12">
+        <v>1</v>
+      </c>
+      <c r="F81" s="2">
+        <v>0</v>
+      </c>
+      <c r="G81" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="D81" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E81" s="14">
-        <v>1</v>
-      </c>
-      <c r="F81" s="2">
-        <v>0</v>
-      </c>
-      <c r="G81" s="4" t="s">
+      <c r="H81" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I81" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="H81" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I81" s="4" t="s">
+      <c r="J81" s="4" t="s">
         <v>293</v>
-      </c>
-      <c r="J81" s="4" t="s">
-        <v>294</v>
       </c>
       <c r="K81" s="2"/>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="C82" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="D82" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="E82" s="12">
+        <v>1</v>
+      </c>
+      <c r="F82" s="2">
+        <v>0</v>
+      </c>
+      <c r="G82" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="E82" s="14">
-        <v>1</v>
-      </c>
-      <c r="F82" s="2">
-        <v>0</v>
-      </c>
-      <c r="G82" s="4" t="s">
+      <c r="H82" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="H82" s="4" t="s">
-        <v>300</v>
-      </c>
       <c r="I82" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K82" s="2"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="C83" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="D83" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="E83" s="12">
+        <v>1</v>
+      </c>
+      <c r="F83" s="2">
+        <v>0</v>
+      </c>
+      <c r="G83" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="E83" s="14">
-        <v>1</v>
-      </c>
-      <c r="F83" s="2">
-        <v>0</v>
-      </c>
-      <c r="G83" s="4" t="s">
+      <c r="H83" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I83" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="H83" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I83" s="4" t="s">
-        <v>306</v>
-      </c>
       <c r="J83" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K83" s="2"/>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="C84" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>309</v>
-      </c>
       <c r="D84" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E84" s="14">
+      <c r="E84" s="12">
         <v>2</v>
       </c>
       <c r="F84" s="2">
         <v>0</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H84" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="K84" s="4" t="s">
         <v>14</v>
@@ -4897,34 +4897,34 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="C85" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="D85" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85" s="12">
+        <v>2</v>
+      </c>
+      <c r="F85" s="2">
+        <v>0</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="D85" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E85" s="14">
-        <v>2</v>
-      </c>
-      <c r="F85" s="2">
-        <v>0</v>
-      </c>
-      <c r="G85" s="4" t="s">
+      <c r="H85" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I85" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="H85" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I85" s="4" t="s">
+      <c r="J85" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="J85" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="K85" s="4" t="s">
         <v>14</v>
@@ -4932,100 +4932,100 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="C86" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="D86" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="E86" s="12">
+        <v>1</v>
+      </c>
+      <c r="F86" s="2">
+        <v>0</v>
+      </c>
+      <c r="G86" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="E86" s="14">
-        <v>1</v>
-      </c>
-      <c r="F86" s="2">
-        <v>0</v>
-      </c>
-      <c r="G86" s="4" t="s">
+      <c r="H86" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I86" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="H86" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I86" s="4" t="s">
-        <v>321</v>
-      </c>
       <c r="J86" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K86" s="2"/>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="C87" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="D87" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E87" s="12">
+        <v>1</v>
+      </c>
+      <c r="F87" s="2">
+        <v>0</v>
+      </c>
+      <c r="G87" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="D87" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="E87" s="14">
-        <v>1</v>
-      </c>
-      <c r="F87" s="2">
-        <v>0</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>325</v>
-      </c>
       <c r="H87" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="J87" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="J87" s="4" t="s">
-        <v>322</v>
       </c>
       <c r="K87" s="2"/>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>327</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>56</v>
       </c>
       <c r="D88" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E88" s="12">
+        <v>16</v>
+      </c>
+      <c r="F88" s="2">
+        <v>0</v>
+      </c>
+      <c r="G88" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="E88" s="14">
-        <v>16</v>
-      </c>
-      <c r="F88" s="2">
-        <v>0</v>
-      </c>
-      <c r="G88" s="4" t="s">
+      <c r="H88" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I88" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="H88" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I88" s="4" t="s">
-        <v>330</v>
-      </c>
       <c r="J88" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>14</v>
@@ -5033,34 +5033,34 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="C89" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="D89" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="D89" s="4" t="s">
+      <c r="E89" s="12">
+        <v>4</v>
+      </c>
+      <c r="F89" s="2">
+        <v>0</v>
+      </c>
+      <c r="G89" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="E89" s="14">
-        <v>4</v>
-      </c>
-      <c r="F89" s="2">
-        <v>0</v>
-      </c>
-      <c r="G89" s="4" t="s">
+      <c r="H89" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="H89" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I89" s="4" t="s">
-        <v>336</v>
-      </c>
       <c r="J89" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K89" s="4" t="s">
         <v>14</v>
@@ -5068,34 +5068,34 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="C90" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="D90" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="E90" s="12">
+        <v>2</v>
+      </c>
+      <c r="F90" s="2">
+        <v>0</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I90" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="E90" s="14">
-        <v>2</v>
-      </c>
-      <c r="F90" s="2">
-        <v>0</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I90" s="4" t="s">
-        <v>341</v>
-      </c>
       <c r="J90" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="K90" s="4" t="s">
         <v>14</v>
@@ -5103,67 +5103,67 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="C91" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="D91" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="E91" s="12">
+        <v>1</v>
+      </c>
+      <c r="F91" s="2">
+        <v>0</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I91" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="E91" s="14">
-        <v>1</v>
-      </c>
-      <c r="F91" s="2">
-        <v>0</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I91" s="4" t="s">
-        <v>346</v>
-      </c>
       <c r="J91" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K91" s="2"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="C92" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="D92" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E92" s="12">
+        <v>4</v>
+      </c>
+      <c r="F92" s="2">
+        <v>0</v>
+      </c>
+      <c r="G92" s="4" t="s">
         <v>349</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E92" s="14">
-        <v>4</v>
-      </c>
-      <c r="F92" s="2">
-        <v>0</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>350</v>
       </c>
       <c r="H92" s="4" t="s">
         <v>67</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K92" s="4" t="s">
         <v>14</v>
@@ -5171,61 +5171,61 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C93" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="D93" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="D93" s="4" t="s">
+      <c r="E93" s="12">
+        <v>1</v>
+      </c>
+      <c r="F93" s="2">
+        <v>0</v>
+      </c>
+      <c r="G93" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="E93" s="14">
-        <v>1</v>
-      </c>
-      <c r="F93" s="2">
-        <v>0</v>
-      </c>
-      <c r="G93" s="4" t="s">
+      <c r="H93" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I93" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="H93" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I93" s="4" t="s">
-        <v>500</v>
-      </c>
       <c r="J93" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="K93" s="4"/>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B94" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="C94" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="D94" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" s="12">
+        <v>4</v>
+      </c>
+      <c r="F94" s="2">
+        <v>0</v>
+      </c>
+      <c r="G94" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="D94" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E94" s="14">
-        <v>4</v>
-      </c>
-      <c r="F94" s="2">
-        <v>0</v>
-      </c>
-      <c r="G94" s="4" t="s">
+      <c r="H94" s="4" t="s">
         <v>355</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>356</v>
       </c>
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
@@ -5235,157 +5235,157 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C95" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="D95" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="D95" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="E95" s="14">
+      <c r="E95" s="12">
         <v>1</v>
       </c>
       <c r="F95" s="2">
         <v>0</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H95" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K95" s="2"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C96" s="4" t="s">
+      <c r="D96" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="D96" s="4" t="s">
+      <c r="E96" s="12">
+        <v>1</v>
+      </c>
+      <c r="F96" s="2">
+        <v>0</v>
+      </c>
+      <c r="G96" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="E96" s="14">
-        <v>1</v>
-      </c>
-      <c r="F96" s="2">
-        <v>0</v>
-      </c>
-      <c r="G96" s="4" t="s">
-        <v>364</v>
-      </c>
       <c r="H96" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K96" s="2"/>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="C97" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="D97" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" s="12">
+        <v>1</v>
+      </c>
+      <c r="F97" s="2">
+        <v>0</v>
+      </c>
+      <c r="G97" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="D97" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E97" s="14">
-        <v>1</v>
-      </c>
-      <c r="F97" s="2">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="s">
+      <c r="H97" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="J97" s="4" t="s">
         <v>368</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I97" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="J97" s="4" t="s">
-        <v>369</v>
       </c>
       <c r="K97" s="2"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="C98" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="D98" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="E98" s="12">
+        <v>1</v>
+      </c>
+      <c r="F98" s="2">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E98" s="14">
-        <v>1</v>
-      </c>
-      <c r="F98" s="2">
-        <v>0</v>
-      </c>
-      <c r="G98" s="4" t="s">
+      <c r="H98" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="J98" s="4" t="s">
         <v>374</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I98" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="J98" s="4" t="s">
-        <v>375</v>
       </c>
       <c r="K98" s="2"/>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="C99" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="C99" s="4" t="s">
-        <v>378</v>
-      </c>
       <c r="D99" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E99" s="14">
+      <c r="E99" s="12">
         <v>1</v>
       </c>
       <c r="F99" s="2">
         <v>0</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H99" s="4" t="s">
         <v>15</v>
@@ -5398,28 +5398,28 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="C100" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="D100" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E100" s="12">
+        <v>1</v>
+      </c>
+      <c r="F100" s="2">
+        <v>0</v>
+      </c>
+      <c r="G100" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="D100" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E100" s="14">
-        <v>1</v>
-      </c>
-      <c r="F100" s="2">
-        <v>0</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>382</v>
-      </c>
       <c r="H100" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
@@ -5427,67 +5427,67 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="C101" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="D101" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E101" s="12">
+        <v>1</v>
+      </c>
+      <c r="F101" s="2">
+        <v>0</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="H101" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="D101" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E101" s="14">
-        <v>1</v>
-      </c>
-      <c r="F101" s="2">
-        <v>0</v>
-      </c>
-      <c r="G101" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="H101" s="4" t="s">
+      <c r="I101" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="I101" s="4" t="s">
-        <v>387</v>
-      </c>
       <c r="J101" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K101" s="2"/>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>389</v>
-      </c>
       <c r="C102" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E102" s="14">
+      <c r="E102" s="12">
         <v>4</v>
       </c>
       <c r="F102" s="2">
         <v>0</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H102" s="4" t="s">
         <v>67</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K102" s="4" t="s">
         <v>14</v>
@@ -5495,67 +5495,67 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="C103" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="D103" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E103" s="12">
+        <v>1</v>
+      </c>
+      <c r="F103" s="2">
+        <v>0</v>
+      </c>
+      <c r="G103" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="D103" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E103" s="14">
-        <v>1</v>
-      </c>
-      <c r="F103" s="2">
-        <v>0</v>
-      </c>
-      <c r="G103" s="4" t="s">
+      <c r="H103" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="J103" s="4" t="s">
         <v>393</v>
-      </c>
-      <c r="H103" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I103" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="J103" s="4" t="s">
-        <v>394</v>
       </c>
       <c r="K103" s="2"/>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="C104" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="C104" s="4" t="s">
-        <v>397</v>
-      </c>
       <c r="D104" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E104" s="14">
+      <c r="E104" s="12">
         <v>6</v>
       </c>
       <c r="F104" s="2">
         <v>0</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H104" s="4" t="s">
         <v>67</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K104" s="4" t="s">
         <v>14</v>
@@ -5563,133 +5563,133 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="C105" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="D105" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="D105" s="4" t="s">
+      <c r="E105" s="12">
+        <v>1</v>
+      </c>
+      <c r="F105" s="2">
+        <v>0</v>
+      </c>
+      <c r="G105" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="E105" s="14">
-        <v>1</v>
-      </c>
-      <c r="F105" s="2">
-        <v>0</v>
-      </c>
-      <c r="G105" s="4" t="s">
+      <c r="H105" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="H105" s="4" t="s">
+      <c r="I105" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="I105" s="4" t="s">
-        <v>405</v>
-      </c>
       <c r="J105" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K105" s="2"/>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="C106" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="D106" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="D106" s="4" t="s">
+      <c r="E106" s="12">
+        <v>1</v>
+      </c>
+      <c r="F106" s="2">
+        <v>0</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I106" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="J106" s="4" t="s">
         <v>409</v>
-      </c>
-      <c r="E106" s="14">
-        <v>1</v>
-      </c>
-      <c r="F106" s="2">
-        <v>0</v>
-      </c>
-      <c r="G106" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="H106" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I106" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="J106" s="4" t="s">
-        <v>410</v>
       </c>
       <c r="K106" s="2"/>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="C107" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="D107" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="D107" s="4" t="s">
+      <c r="E107" s="12">
+        <v>1</v>
+      </c>
+      <c r="F107" s="2">
+        <v>0</v>
+      </c>
+      <c r="G107" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="E107" s="14">
-        <v>1</v>
-      </c>
-      <c r="F107" s="2">
-        <v>0</v>
-      </c>
-      <c r="G107" s="4" t="s">
+      <c r="H107" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="I107" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="J107" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="H107" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="I107" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="J107" s="4" t="s">
-        <v>416</v>
       </c>
       <c r="K107" s="2"/>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="C108" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="D108" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="E108" s="12">
+        <v>3</v>
+      </c>
+      <c r="F108" s="2">
+        <v>0</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="H108" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="E108" s="14">
-        <v>3</v>
-      </c>
-      <c r="F108" s="2">
-        <v>0</v>
-      </c>
-      <c r="G108" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="H108" s="4" t="s">
-        <v>421</v>
-      </c>
       <c r="I108" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="K108" s="4" t="s">
         <v>14</v>
@@ -5697,58 +5697,58 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B109" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="C109" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="D109" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="D109" s="4" t="s">
+      <c r="E109" s="12">
+        <v>1</v>
+      </c>
+      <c r="F109" s="2">
+        <v>0</v>
+      </c>
+      <c r="G109" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="E109" s="14">
-        <v>1</v>
-      </c>
-      <c r="F109" s="2">
-        <v>0</v>
-      </c>
-      <c r="G109" s="4" t="s">
-        <v>426</v>
-      </c>
       <c r="H109" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="K109" s="2"/>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="C110" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="D110" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="D110" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="E110" s="14">
+      <c r="E110" s="12">
         <v>2</v>
       </c>
       <c r="F110" s="2">
         <v>0</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H110" s="4" t="s">
         <v>15</v>
@@ -5757,7 +5757,7 @@
         <v>68</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="K110" s="4" t="s">
         <v>14</v>
@@ -5765,34 +5765,34 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="C111" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="D111" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="D111" s="4" t="s">
+      <c r="E111" s="12">
+        <v>9</v>
+      </c>
+      <c r="F111" s="2">
+        <v>0</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I111" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="E111" s="14">
-        <v>9</v>
-      </c>
-      <c r="F111" s="2">
-        <v>0</v>
-      </c>
-      <c r="G111" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I111" s="4" t="s">
-        <v>435</v>
-      </c>
       <c r="J111" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="K111" s="4" t="s">
         <v>14</v>
@@ -5800,34 +5800,34 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="C112" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="D112" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="D112" s="4" t="s">
+      <c r="E112" s="12">
+        <v>4</v>
+      </c>
+      <c r="F112" s="2">
+        <v>0</v>
+      </c>
+      <c r="G112" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="E112" s="14">
-        <v>4</v>
-      </c>
-      <c r="F112" s="2">
-        <v>0</v>
-      </c>
-      <c r="G112" s="4" t="s">
+      <c r="H112" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I112" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="H112" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I112" s="4" t="s">
+      <c r="J112" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="J112" s="4" t="s">
-        <v>442</v>
       </c>
       <c r="K112" s="4" t="s">
         <v>14</v>
@@ -5835,133 +5835,133 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="C113" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D113" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="C113" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="D113" s="4" t="s">
+      <c r="E113" s="12">
+        <v>1</v>
+      </c>
+      <c r="F113" s="2">
+        <v>0</v>
+      </c>
+      <c r="G113" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="E113" s="14">
-        <v>1</v>
-      </c>
-      <c r="F113" s="2">
-        <v>0</v>
-      </c>
-      <c r="G113" s="4" t="s">
-        <v>446</v>
-      </c>
       <c r="H113" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="K113" s="2"/>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="C114" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="D114" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E114" s="12">
+        <v>1</v>
+      </c>
+      <c r="F114" s="2">
+        <v>0</v>
+      </c>
+      <c r="G114" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="D114" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E114" s="14">
-        <v>1</v>
-      </c>
-      <c r="F114" s="2">
-        <v>0</v>
-      </c>
-      <c r="G114" s="4" t="s">
+      <c r="H114" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="H114" s="4" t="s">
-        <v>451</v>
-      </c>
       <c r="I114" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="K114" s="2"/>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="C115" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E115" s="12">
+        <v>1</v>
+      </c>
+      <c r="F115" s="2">
+        <v>0</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="H115" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="C115" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="D115" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E115" s="14">
-        <v>1</v>
-      </c>
-      <c r="F115" s="2">
-        <v>0</v>
-      </c>
-      <c r="G115" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>454</v>
-      </c>
       <c r="I115" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K115" s="2"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="C116" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="D116" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="D116" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="E116" s="14">
+      <c r="E116" s="12">
         <v>2</v>
       </c>
       <c r="F116" s="2">
         <v>0</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H116" s="4" t="s">
         <v>67</v>
       </c>
       <c r="I116" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K116" s="4" t="s">
         <v>14</v>
@@ -5969,67 +5969,67 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="C117" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="D117" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="D117" s="4" t="s">
+      <c r="E117" s="12">
+        <v>1</v>
+      </c>
+      <c r="F117" s="2">
+        <v>0</v>
+      </c>
+      <c r="G117" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="E117" s="14">
-        <v>1</v>
-      </c>
-      <c r="F117" s="2">
-        <v>0</v>
-      </c>
-      <c r="G117" s="4" t="s">
-        <v>463</v>
-      </c>
       <c r="H117" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K117" s="2"/>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="B118" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="C118" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="C118" s="4" t="s">
-        <v>466</v>
-      </c>
       <c r="D118" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E118" s="14">
+      <c r="E118" s="12">
         <v>7</v>
       </c>
       <c r="F118" s="2">
         <v>0</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H118" s="4" t="s">
         <v>67</v>
       </c>
       <c r="I118" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J118" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K118" s="4" t="s">
         <v>14</v>
@@ -6037,34 +6037,34 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="C119" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D119" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="C119" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="D119" s="4" t="s">
+      <c r="E119" s="12">
+        <v>2</v>
+      </c>
+      <c r="F119" s="2">
+        <v>0</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="H119" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="E119" s="14">
-        <v>2</v>
-      </c>
-      <c r="F119" s="2">
-        <v>0</v>
-      </c>
-      <c r="G119" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="H119" s="4" t="s">
-        <v>470</v>
-      </c>
       <c r="I119" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J119" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K119" s="4" t="s">
         <v>14</v>
